--- a/Valuaciones_USA/CI_razones_financieras.xlsx
+++ b/Valuaciones_USA/CI_razones_financieras.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="395">
   <si>
     <t>Calculo</t>
   </si>
@@ -82,12 +82,21 @@
     <t>Sep2025</t>
   </si>
   <si>
+    <t>Amortizacion(%)</t>
+  </si>
+  <si>
     <t>Net Profit Margin(%)</t>
   </si>
   <si>
     <t>Net Income</t>
   </si>
   <si>
+    <t>Gross Profit(%)</t>
+  </si>
+  <si>
+    <t>Operating Margin(%)</t>
+  </si>
+  <si>
     <t>EPS</t>
   </si>
   <si>
@@ -106,7 +115,19 @@
     <t>Sales Growth</t>
   </si>
   <si>
-    <t>Net Interest Margin (Bank Only) %</t>
+    <t>Cost of Goods Sold</t>
+  </si>
+  <si>
+    <t>Cost of Goods Sold Growth</t>
+  </si>
+  <si>
+    <t>Inventories</t>
+  </si>
+  <si>
+    <t>Inventories Growth</t>
+  </si>
+  <si>
+    <t>Inventory Turnover Ratio</t>
   </si>
   <si>
     <t>Dividends per Share</t>
@@ -136,12 +157,21 @@
     <t>Pasivo/Fondos Propios</t>
   </si>
   <si>
+    <t>Current Ratio</t>
+  </si>
+  <si>
     <t>long-term debt-to-equity(%)</t>
   </si>
   <si>
     <t>Gasto financiero(%)</t>
   </si>
   <si>
+    <t>Inventory to current Assets(%)</t>
+  </si>
+  <si>
+    <t>Net Trading Cycle</t>
+  </si>
+  <si>
     <t>PEGY Ratio</t>
   </si>
   <si>
@@ -151,6 +181,9 @@
     <t>P/S Ratio</t>
   </si>
   <si>
+    <t>Receivable to Current Assets(%)</t>
+  </si>
+  <si>
     <t>ROA%</t>
   </si>
   <si>
@@ -160,10 +193,13 @@
     <t>ROB</t>
   </si>
   <si>
+    <t>ROIC %</t>
+  </si>
+  <si>
     <t>WACC %</t>
   </si>
   <si>
-    <t>WACC % Growth</t>
+    <t>Test de Acidez</t>
   </si>
   <si>
     <t>Valor en libros</t>
@@ -172,24 +208,24 @@
     <t>Piotrivski F-Score</t>
   </si>
   <si>
+    <t>Altman Z score</t>
+  </si>
+  <si>
     <t>Beneish M-Score</t>
   </si>
   <si>
-    <t>Return-on-Tangible-Equity</t>
-  </si>
-  <si>
-    <t>Efficiency Ratio(%)</t>
-  </si>
-  <si>
-    <t>Equity-to-Asset</t>
-  </si>
-  <si>
-    <t>Loan to Deposit Ratio(%)</t>
+    <t>Amortization/ gross profit</t>
   </si>
   <si>
     <t>Net income / sales</t>
   </si>
   <si>
+    <t>Gross profit/sales</t>
+  </si>
+  <si>
+    <t>Operating profit/sales</t>
+  </si>
+  <si>
     <t>Net Income/Shares</t>
   </si>
   <si>
@@ -199,6 +235,9 @@
     <t>Crecimiento vs año pasado</t>
   </si>
   <si>
+    <t>Cost of Goods Sold / Inventories</t>
+  </si>
+  <si>
     <t>FCF/Sales</t>
   </si>
   <si>
@@ -223,6 +262,12 @@
     <t>net interest income(expenses)/operating income</t>
   </si>
   <si>
+    <t>inventories/current asset</t>
+  </si>
+  <si>
+    <t>Rotación de cuentas por cobrar + Rotación de inventarios - Rotación de cuentas por pagar</t>
+  </si>
+  <si>
     <t>P/E ratio/ EPS growth rate+dividend yield</t>
   </si>
   <si>
@@ -232,6 +277,9 @@
     <t>market cap / sales</t>
   </si>
   <si>
+    <t>accounts receivable/current asset</t>
+  </si>
+  <si>
     <t>net income 2020/((total assets 2019+total assets 2020)/2)</t>
   </si>
   <si>
@@ -241,13 +289,17 @@
     <t>Total assets 2020/ ((shareholders equity 2019+shareholders equity 2020)/2)</t>
   </si>
   <si>
+    <t>Operating income * (1-tax rate %) / ((total assets - accounts payable y acrued expense - (cash, cash equivalents y marketable securities - max(0,total current liabilities - total current assets + cash,cash equivalents, marketable securities))</t>
+  </si>
+  <si>
+    <t>(Current assets-inventory)/current liabilities</t>
+  </si>
+  <si>
     <t>Stockholders equity - preferred stock / average shares outstanding</t>
   </si>
   <si>
-    <t>Total Noninterest Expense / (Net Interest Income + Non Interest Income)</t>
-  </si>
-  <si>
-    <t>Net Loan / Total Deposits</t>
+    <t>* Una empresa con menor a 10% es bueno
+* Más del 20% indica mucha competencia en el sector</t>
   </si>
   <si>
     <t>* Algo mayor a 20% indica una ventaja 
@@ -259,6 +311,13 @@
     <t>Se busca tendencia alcista</t>
   </si>
   <si>
+    <t>* Un porcentaje mayor a 40% indica cierta ventaja
+* Porcentajes menores a 40% en un sector significa demasiada competencia y algo menor al 20% en una industria indica dificultad de crear ventaja</t>
+  </si>
+  <si>
+    <t>Se busca tendencia alcista o estable</t>
+  </si>
+  <si>
     <t>Se busca tendencia a la alza en los ultimos 5 0 10 años</t>
   </si>
   <si>
@@ -268,7 +327,21 @@
     <t>Se busca porcentajes estables o en crecimiento</t>
   </si>
   <si>
-    <t>Mayor a 3.5 % es bueno , una tendencia a la baja es mala</t>
+    <t>Se busca tendencia bajista o que incrementen menos que las sales</t>
+  </si>
+  <si>
+    <t>Se busca que crezca a menor porcentaje que las Sales</t>
+  </si>
+  <si>
+    <t>se busca crecimiento estable</t>
+  </si>
+  <si>
+    <t>Se busca crecimiento estable</t>
+  </si>
+  <si>
+    <t>*Un valor mayor a 8 indica excelencia
+ *Un valor entre 4 y 8 indica rango saludable
+*Menor a 4 indica baja rotación</t>
   </si>
   <si>
     <t>Buscar tendencia alcista</t>
@@ -294,6 +367,11 @@
   <si>
     <t>Si algo es menor a 1 es mejor
 * Para las financiera un relación menor a .80 es una ventaja competitiva</t>
+  </si>
+  <si>
+    <t>*En teoría algo mayor a 1 indica solvencia, pero existen empresas con algo menor a 1 que debido a su rentabilidad pueden cubrir el pasivo
+*Algo mayor a 1.5 puede ser muy bueno
+*evitar aquellas menores a .5</t>
   </si>
   <si>
     <t>Se busca un balance de 75% capital, 25% deuda
@@ -303,6 +381,12 @@
     <t>* Un gasto menor a 15% indica una ventaja
 * En el area financiera un porcentaje bajo puede ser un 30%
 *En cualquier industria la empresa con la proporción más baja tiene la ventaja</t>
+  </si>
+  <si>
+    <t>Buscar compañias con un rango menor al 40% y evitar empresas con algo mayor al 60%</t>
+  </si>
+  <si>
+    <t>Entre menor sea, mejor, buscar una tendencia bajista,un valor negativo es bueno siempre y cuando el revenue continue subiendo</t>
   </si>
   <si>
     <t>*No es efectivo para empresas que pagan más de un 8% de dividendo,Buscar que sea menor a 1</t>
@@ -331,10 +415,14 @@
     <t>ratios mayores a 4.5 vuelve a las empresas riesgosas</t>
   </si>
   <si>
-    <t>Costo que tiene la obtencion del capital, entre menor sea mejor</t>
-  </si>
-  <si>
-    <t>Se busca porcentajes estables o en bajada</t>
+    <t>Si es mayor a su WACC indica que genera más dinero que lo que paga por el
+Si tiene un ROIC mayor al 15% tiene una ventaja competitiva</t>
+  </si>
+  <si>
+    <t>Costo que tiene la obtencion del capital, entre menor sea mejor,debe ser menor al ROIC</t>
+  </si>
+  <si>
+    <t>Un indice mayor a 1 coloca a la empresa en buena posición</t>
   </si>
   <si>
     <t>*Comprar acciones que no pase su valor en 1.5
@@ -347,20 +435,16 @@
 * Mal o bajo score entre 0,1,2,3</t>
   </si>
   <si>
+    <t>*Algo menor a 1.8 es malo ya que indica que la empresa podria entrar en bancarrota en los proximos dos años
+* entre 1.8 y 3 es zona griss
+* mayor a 3 es zona segura e indica una alta fuerza financiera</t>
+  </si>
+  <si>
     <t>* Menor a 1.78 indica que podrian manipular sus estados financieros.
 * Mayor a 1.78, podria indicar que no manipulan sus estados financieros</t>
   </si>
   <si>
-    <t>* Mayor a 15% es bueno,10% es aceptable,&lt; 5% es malo</t>
-  </si>
-  <si>
-    <t>Menor a 50% es excelente, menor a 60% es bueno,mayor a 65-70% indica una estructura de costos alta</t>
-  </si>
-  <si>
-    <t>* Mayor a 10% es bueno, menor a 6% indica apalancamiento</t>
-  </si>
-  <si>
-    <t>Entre 80-90 % es bueno, mayor a 100% indica que la empresa esta prestando más de lo que tiene en depósitos y menor a 70% indica que la empresa no esta prestando lo suficiente</t>
+    <t>N/A</t>
   </si>
   <si>
     <t>6.98</t>
@@ -375,9 +459,6 @@
     <t>0.00</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>2.99</t>
   </si>
   <si>
@@ -444,9 +525,6 @@
     <t>8.44</t>
   </si>
   <si>
-    <t>-24.74</t>
-  </si>
-  <si>
     <t>1.53</t>
   </si>
   <si>
@@ -489,9 +567,6 @@
     <t>11.51</t>
   </si>
   <si>
-    <t>27.99</t>
-  </si>
-  <si>
     <t>7.07</t>
   </si>
   <si>
@@ -534,9 +609,6 @@
     <t>7.92</t>
   </si>
   <si>
-    <t>6.93</t>
-  </si>
-  <si>
     <t>6.07</t>
   </si>
   <si>
@@ -579,9 +651,6 @@
     <t>6.86</t>
   </si>
   <si>
-    <t>-9.39</t>
-  </si>
-  <si>
     <t>5.82</t>
   </si>
   <si>
@@ -624,9 +693,6 @@
     <t>6.34</t>
   </si>
   <si>
-    <t>-51.01</t>
-  </si>
-  <si>
     <t>5.57</t>
   </si>
   <si>
@@ -669,9 +735,6 @@
     <t>5.44</t>
   </si>
   <si>
-    <t>-29.03</t>
-  </si>
-  <si>
     <t>4.56</t>
   </si>
   <si>
@@ -711,9 +774,6 @@
     <t>5.09</t>
   </si>
   <si>
-    <t>71.24</t>
-  </si>
-  <si>
     <t>6.02</t>
   </si>
   <si>
@@ -753,9 +813,6 @@
     <t>5.14</t>
   </si>
   <si>
-    <t>-16.18</t>
-  </si>
-  <si>
     <t>5.53</t>
   </si>
   <si>
@@ -795,9 +852,6 @@
     <t>4.71</t>
   </si>
   <si>
-    <t>-32.54</t>
-  </si>
-  <si>
     <t>4.67</t>
   </si>
   <si>
@@ -840,9 +894,6 @@
     <t>4.31</t>
   </si>
   <si>
-    <t>13.62</t>
-  </si>
-  <si>
     <t>5.32</t>
   </si>
   <si>
@@ -882,9 +933,6 @@
     <t>4.49</t>
   </si>
   <si>
-    <t>4.32</t>
-  </si>
-  <si>
     <t>5.43</t>
   </si>
   <si>
@@ -927,9 +975,6 @@
     <t>3.73</t>
   </si>
   <si>
-    <t>82.99</t>
-  </si>
-  <si>
     <t>3.32</t>
   </si>
   <si>
@@ -966,9 +1011,6 @@
     <t>3.43</t>
   </si>
   <si>
-    <t>-18.34</t>
-  </si>
-  <si>
     <t>5.27</t>
   </si>
   <si>
@@ -1008,9 +1050,6 @@
     <t>3.09</t>
   </si>
   <si>
-    <t>-21.23</t>
-  </si>
-  <si>
     <t>3.08</t>
   </si>
   <si>
@@ -1050,9 +1089,6 @@
     <t>3.28</t>
   </si>
   <si>
-    <t>10.16</t>
-  </si>
-  <si>
     <t>3.72</t>
   </si>
   <si>
@@ -1086,9 +1122,6 @@
     <t>3.22</t>
   </si>
   <si>
-    <t>13.12</t>
-  </si>
-  <si>
     <t>8.70</t>
   </si>
   <si>
@@ -1119,9 +1152,6 @@
     <t>3.30</t>
   </si>
   <si>
-    <t>-16.14</t>
-  </si>
-  <si>
     <t>1.41</t>
   </si>
   <si>
@@ -1198,9 +1228,6 @@
   </si>
   <si>
     <t>3.76</t>
-  </si>
-  <si>
-    <t>-24.30</t>
   </si>
 </sst>
 </file>
@@ -1558,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:W45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1634,209 +1661,209 @@
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="H2" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="I2" t="s">
-        <v>182</v>
+        <v>133</v>
       </c>
       <c r="J2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="K2" t="s">
-        <v>212</v>
+        <v>133</v>
       </c>
       <c r="L2" t="s">
-        <v>226</v>
+        <v>133</v>
       </c>
       <c r="M2" t="s">
-        <v>240</v>
+        <v>133</v>
       </c>
       <c r="N2" t="s">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="O2" t="s">
-        <v>269</v>
+        <v>133</v>
       </c>
       <c r="P2" t="s">
-        <v>283</v>
+        <v>133</v>
       </c>
       <c r="Q2" t="s">
-        <v>298</v>
+        <v>133</v>
       </c>
       <c r="R2" t="s">
-        <v>311</v>
+        <v>133</v>
       </c>
       <c r="S2" t="s">
-        <v>325</v>
+        <v>133</v>
       </c>
       <c r="T2" t="s">
-        <v>339</v>
+        <v>133</v>
       </c>
       <c r="U2" t="s">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="V2" t="s">
-        <v>362</v>
+        <v>133</v>
       </c>
       <c r="W2" t="s">
-        <v>375</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="B3" t="s">
+        <v>67</v>
+      </c>
       <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3">
-        <v>1155</v>
-      </c>
-      <c r="E3">
-        <v>1115</v>
-      </c>
-      <c r="F3">
-        <v>292</v>
-      </c>
-      <c r="G3">
-        <v>1302</v>
-      </c>
-      <c r="H3">
-        <v>1279</v>
-      </c>
-      <c r="I3">
-        <v>1260</v>
-      </c>
-      <c r="J3">
-        <v>1623</v>
-      </c>
-      <c r="K3">
-        <v>1476</v>
-      </c>
-      <c r="L3">
-        <v>2102</v>
-      </c>
-      <c r="M3">
-        <v>2094</v>
-      </c>
-      <c r="N3">
-        <v>1867</v>
-      </c>
-      <c r="O3">
-        <v>2237</v>
-      </c>
-      <c r="P3">
-        <v>2637</v>
-      </c>
-      <c r="Q3">
-        <v>5104</v>
-      </c>
-      <c r="R3">
-        <v>8458</v>
-      </c>
-      <c r="S3">
-        <v>5370</v>
-      </c>
-      <c r="T3">
-        <v>6704</v>
-      </c>
-      <c r="U3">
-        <v>5164</v>
-      </c>
-      <c r="V3">
-        <v>3434</v>
-      </c>
-      <c r="W3">
-        <v>6147</v>
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H3" t="s">
+        <v>188</v>
+      </c>
+      <c r="I3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K3" t="s">
+        <v>230</v>
+      </c>
+      <c r="L3" t="s">
+        <v>243</v>
+      </c>
+      <c r="M3" t="s">
+        <v>256</v>
+      </c>
+      <c r="N3" t="s">
+        <v>269</v>
+      </c>
+      <c r="O3" t="s">
+        <v>283</v>
+      </c>
+      <c r="P3" t="s">
+        <v>296</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>310</v>
+      </c>
+      <c r="R3" t="s">
+        <v>322</v>
+      </c>
+      <c r="S3" t="s">
+        <v>335</v>
+      </c>
+      <c r="T3" t="s">
+        <v>348</v>
+      </c>
+      <c r="U3" t="s">
+        <v>206</v>
+      </c>
+      <c r="V3" t="s">
+        <v>369</v>
+      </c>
+      <c r="W3" t="s">
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:23">
       <c r="A4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
-        <v>58</v>
-      </c>
       <c r="C4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E4" t="s">
-        <v>124</v>
-      </c>
-      <c r="F4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" t="s">
-        <v>168</v>
-      </c>
-      <c r="I4" t="s">
-        <v>183</v>
-      </c>
-      <c r="J4" t="s">
-        <v>198</v>
-      </c>
-      <c r="K4" t="s">
-        <v>213</v>
-      </c>
-      <c r="L4" t="s">
-        <v>227</v>
-      </c>
-      <c r="M4" t="s">
-        <v>241</v>
-      </c>
-      <c r="N4" t="s">
-        <v>255</v>
-      </c>
-      <c r="O4" t="s">
-        <v>270</v>
-      </c>
-      <c r="P4" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>299</v>
-      </c>
-      <c r="R4" t="s">
-        <v>312</v>
-      </c>
-      <c r="S4" t="s">
-        <v>326</v>
-      </c>
-      <c r="T4" t="s">
-        <v>340</v>
-      </c>
-      <c r="U4" t="s">
-        <v>351</v>
-      </c>
-      <c r="V4" t="s">
-        <v>363</v>
-      </c>
-      <c r="W4" t="s">
-        <v>376</v>
+        <v>96</v>
+      </c>
+      <c r="D4">
+        <v>1155</v>
+      </c>
+      <c r="E4">
+        <v>1115</v>
+      </c>
+      <c r="F4">
+        <v>292</v>
+      </c>
+      <c r="G4">
+        <v>1302</v>
+      </c>
+      <c r="H4">
+        <v>1279</v>
+      </c>
+      <c r="I4">
+        <v>1260</v>
+      </c>
+      <c r="J4">
+        <v>1623</v>
+      </c>
+      <c r="K4">
+        <v>1476</v>
+      </c>
+      <c r="L4">
+        <v>2102</v>
+      </c>
+      <c r="M4">
+        <v>2094</v>
+      </c>
+      <c r="N4">
+        <v>1867</v>
+      </c>
+      <c r="O4">
+        <v>2237</v>
+      </c>
+      <c r="P4">
+        <v>2637</v>
+      </c>
+      <c r="Q4">
+        <v>5104</v>
+      </c>
+      <c r="R4">
+        <v>8458</v>
+      </c>
+      <c r="S4">
+        <v>5370</v>
+      </c>
+      <c r="T4">
+        <v>6704</v>
+      </c>
+      <c r="U4">
+        <v>5164</v>
+      </c>
+      <c r="V4">
+        <v>3434</v>
+      </c>
+      <c r="W4">
+        <v>6147</v>
       </c>
     </row>
     <row r="5" spans="1:23">
@@ -1844,206 +1871,212 @@
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="F5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="H5" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="I5" t="s">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="J5" t="s">
-        <v>199</v>
+        <v>133</v>
       </c>
       <c r="K5" t="s">
-        <v>214</v>
+        <v>133</v>
       </c>
       <c r="L5" t="s">
-        <v>228</v>
+        <v>133</v>
       </c>
       <c r="M5" t="s">
-        <v>242</v>
+        <v>133</v>
       </c>
       <c r="N5" t="s">
-        <v>256</v>
+        <v>133</v>
       </c>
       <c r="O5" t="s">
-        <v>271</v>
+        <v>133</v>
       </c>
       <c r="P5" t="s">
-        <v>285</v>
+        <v>133</v>
       </c>
       <c r="Q5" t="s">
-        <v>300</v>
+        <v>133</v>
       </c>
       <c r="R5" t="s">
-        <v>313</v>
+        <v>133</v>
       </c>
       <c r="S5" t="s">
-        <v>327</v>
+        <v>133</v>
       </c>
       <c r="T5" t="s">
-        <v>341</v>
+        <v>133</v>
       </c>
       <c r="U5" t="s">
-        <v>352</v>
+        <v>133</v>
       </c>
       <c r="V5" t="s">
-        <v>364</v>
+        <v>133</v>
       </c>
       <c r="W5" t="s">
-        <v>377</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:23">
       <c r="A6" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="B6" t="s">
+        <v>69</v>
+      </c>
       <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6">
-        <v>336.735</v>
-      </c>
-      <c r="E6">
-        <v>283.191</v>
-      </c>
-      <c r="F6">
-        <v>278.843</v>
-      </c>
-      <c r="G6">
-        <v>275.357</v>
-      </c>
-      <c r="H6">
-        <v>275.287</v>
-      </c>
-      <c r="I6">
-        <v>274.249</v>
-      </c>
-      <c r="J6">
-        <v>289.53</v>
-      </c>
-      <c r="K6">
-        <v>284.685</v>
-      </c>
-      <c r="L6">
-        <v>268.603</v>
-      </c>
-      <c r="M6">
-        <v>260.592</v>
-      </c>
-      <c r="N6">
-        <v>259.647</v>
-      </c>
-      <c r="O6">
-        <v>255.072</v>
-      </c>
-      <c r="P6">
-        <v>246.652</v>
-      </c>
-      <c r="Q6">
-        <v>379.817</v>
-      </c>
-      <c r="R6">
-        <v>368.389</v>
-      </c>
-      <c r="S6">
-        <v>340.966</v>
-      </c>
-      <c r="T6">
-        <v>313.065</v>
-      </c>
-      <c r="U6">
-        <v>296.882</v>
-      </c>
-      <c r="V6">
-        <v>283.218</v>
-      </c>
-      <c r="W6">
-        <v>267.53</v>
+        <v>98</v>
+      </c>
+      <c r="D6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" t="s">
+        <v>133</v>
+      </c>
+      <c r="J6" t="s">
+        <v>133</v>
+      </c>
+      <c r="K6" t="s">
+        <v>133</v>
+      </c>
+      <c r="L6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M6" t="s">
+        <v>133</v>
+      </c>
+      <c r="N6" t="s">
+        <v>133</v>
+      </c>
+      <c r="O6" t="s">
+        <v>133</v>
+      </c>
+      <c r="P6" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>133</v>
+      </c>
+      <c r="R6" t="s">
+        <v>133</v>
+      </c>
+      <c r="S6" t="s">
+        <v>133</v>
+      </c>
+      <c r="T6" t="s">
+        <v>133</v>
+      </c>
+      <c r="U6" t="s">
+        <v>133</v>
+      </c>
+      <c r="V6" t="s">
+        <v>133</v>
+      </c>
+      <c r="W6" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:23">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
       <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7">
-        <v>16547</v>
-      </c>
-      <c r="E7">
-        <v>17623</v>
-      </c>
-      <c r="F7">
-        <v>19101</v>
-      </c>
-      <c r="G7">
-        <v>18414</v>
-      </c>
-      <c r="H7">
-        <v>21073</v>
-      </c>
-      <c r="I7">
-        <v>21631</v>
-      </c>
-      <c r="J7">
-        <v>29119</v>
-      </c>
-      <c r="K7">
-        <v>32380</v>
-      </c>
-      <c r="L7">
-        <v>34914</v>
-      </c>
-      <c r="M7">
-        <v>37876</v>
-      </c>
-      <c r="N7">
-        <v>40007</v>
-      </c>
-      <c r="O7">
-        <v>42043</v>
-      </c>
-      <c r="P7">
-        <v>48569</v>
-      </c>
-      <c r="Q7">
-        <v>153743</v>
-      </c>
-      <c r="R7">
-        <v>160550</v>
-      </c>
-      <c r="S7">
-        <v>174267</v>
-      </c>
-      <c r="T7">
-        <v>180031</v>
-      </c>
-      <c r="U7">
-        <v>195187</v>
-      </c>
-      <c r="V7">
-        <v>244384</v>
-      </c>
-      <c r="W7">
-        <v>267933</v>
+        <v>99</v>
+      </c>
+      <c r="D7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G7" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" t="s">
+        <v>189</v>
+      </c>
+      <c r="I7" t="s">
+        <v>203</v>
+      </c>
+      <c r="J7" t="s">
+        <v>217</v>
+      </c>
+      <c r="K7" t="s">
+        <v>231</v>
+      </c>
+      <c r="L7" t="s">
+        <v>244</v>
+      </c>
+      <c r="M7" t="s">
+        <v>257</v>
+      </c>
+      <c r="N7" t="s">
+        <v>270</v>
+      </c>
+      <c r="O7" t="s">
+        <v>284</v>
+      </c>
+      <c r="P7" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>311</v>
+      </c>
+      <c r="R7" t="s">
+        <v>323</v>
+      </c>
+      <c r="S7" t="s">
+        <v>336</v>
+      </c>
+      <c r="T7" t="s">
+        <v>349</v>
+      </c>
+      <c r="U7" t="s">
+        <v>359</v>
+      </c>
+      <c r="V7" t="s">
+        <v>370</v>
+      </c>
+      <c r="W7" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -2051,141 +2084,138 @@
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>149</v>
       </c>
       <c r="F8" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="G8" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="H8" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="I8" t="s">
-        <v>185</v>
+        <v>204</v>
       </c>
       <c r="J8" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="K8" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="L8" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="M8" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="N8" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="O8" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="P8" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="Q8" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="R8" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="S8" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="T8" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="U8" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="V8" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="W8" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9" spans="1:23">
       <c r="A9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
-        <v>60</v>
-      </c>
       <c r="C9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" t="s">
-        <v>127</v>
-      </c>
-      <c r="F9" t="s">
-        <v>141</v>
-      </c>
-      <c r="G9" t="s">
-        <v>156</v>
-      </c>
-      <c r="H9" t="s">
-        <v>171</v>
-      </c>
-      <c r="I9" t="s">
-        <v>186</v>
-      </c>
-      <c r="J9" t="s">
-        <v>201</v>
-      </c>
-      <c r="K9" t="s">
-        <v>216</v>
-      </c>
-      <c r="L9" t="s">
-        <v>230</v>
-      </c>
-      <c r="M9" t="s">
-        <v>244</v>
-      </c>
-      <c r="N9" t="s">
-        <v>258</v>
-      </c>
-      <c r="O9" t="s">
-        <v>224</v>
-      </c>
-      <c r="P9" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>302</v>
-      </c>
-      <c r="R9" t="s">
-        <v>315</v>
-      </c>
-      <c r="S9" t="s">
-        <v>329</v>
-      </c>
-      <c r="T9" t="s">
-        <v>265</v>
-      </c>
-      <c r="U9" t="s">
-        <v>354</v>
-      </c>
-      <c r="V9" t="s">
-        <v>366</v>
-      </c>
-      <c r="W9" t="s">
-        <v>379</v>
+        <v>100</v>
+      </c>
+      <c r="D9">
+        <v>336.735</v>
+      </c>
+      <c r="E9">
+        <v>283.191</v>
+      </c>
+      <c r="F9">
+        <v>278.843</v>
+      </c>
+      <c r="G9">
+        <v>275.357</v>
+      </c>
+      <c r="H9">
+        <v>275.287</v>
+      </c>
+      <c r="I9">
+        <v>274.249</v>
+      </c>
+      <c r="J9">
+        <v>289.53</v>
+      </c>
+      <c r="K9">
+        <v>284.685</v>
+      </c>
+      <c r="L9">
+        <v>268.603</v>
+      </c>
+      <c r="M9">
+        <v>260.592</v>
+      </c>
+      <c r="N9">
+        <v>259.647</v>
+      </c>
+      <c r="O9">
+        <v>255.072</v>
+      </c>
+      <c r="P9">
+        <v>246.652</v>
+      </c>
+      <c r="Q9">
+        <v>379.817</v>
+      </c>
+      <c r="R9">
+        <v>368.389</v>
+      </c>
+      <c r="S9">
+        <v>340.966</v>
+      </c>
+      <c r="T9">
+        <v>313.065</v>
+      </c>
+      <c r="U9">
+        <v>296.882</v>
+      </c>
+      <c r="V9">
+        <v>283.218</v>
+      </c>
+      <c r="W9">
+        <v>267.53</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -2193,274 +2223,277 @@
         <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10" t="s">
-        <v>113</v>
-      </c>
-      <c r="G10" t="s">
-        <v>113</v>
-      </c>
-      <c r="H10" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" t="s">
-        <v>113</v>
-      </c>
-      <c r="K10" t="s">
-        <v>113</v>
-      </c>
-      <c r="L10" t="s">
-        <v>113</v>
-      </c>
-      <c r="M10" t="s">
-        <v>113</v>
-      </c>
-      <c r="N10" t="s">
-        <v>113</v>
-      </c>
-      <c r="O10" t="s">
-        <v>113</v>
-      </c>
-      <c r="P10" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>113</v>
-      </c>
-      <c r="R10" t="s">
-        <v>113</v>
-      </c>
-      <c r="S10" t="s">
-        <v>113</v>
-      </c>
-      <c r="T10" t="s">
-        <v>113</v>
-      </c>
-      <c r="U10" t="s">
-        <v>113</v>
-      </c>
-      <c r="V10" t="s">
-        <v>113</v>
-      </c>
-      <c r="W10" t="s">
-        <v>113</v>
+        <v>96</v>
+      </c>
+      <c r="D10">
+        <v>16547</v>
+      </c>
+      <c r="E10">
+        <v>17623</v>
+      </c>
+      <c r="F10">
+        <v>19101</v>
+      </c>
+      <c r="G10">
+        <v>18414</v>
+      </c>
+      <c r="H10">
+        <v>21073</v>
+      </c>
+      <c r="I10">
+        <v>21631</v>
+      </c>
+      <c r="J10">
+        <v>29119</v>
+      </c>
+      <c r="K10">
+        <v>32380</v>
+      </c>
+      <c r="L10">
+        <v>34914</v>
+      </c>
+      <c r="M10">
+        <v>37876</v>
+      </c>
+      <c r="N10">
+        <v>40007</v>
+      </c>
+      <c r="O10">
+        <v>42043</v>
+      </c>
+      <c r="P10">
+        <v>48569</v>
+      </c>
+      <c r="Q10">
+        <v>153743</v>
+      </c>
+      <c r="R10">
+        <v>160550</v>
+      </c>
+      <c r="S10">
+        <v>174267</v>
+      </c>
+      <c r="T10">
+        <v>180031</v>
+      </c>
+      <c r="U10">
+        <v>195187</v>
+      </c>
+      <c r="V10">
+        <v>244384</v>
+      </c>
+      <c r="W10">
+        <v>267933</v>
       </c>
     </row>
     <row r="11" spans="1:23">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
       <c r="C11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11">
-        <v>0.033</v>
-      </c>
-      <c r="E11">
-        <v>0.038</v>
-      </c>
-      <c r="F11">
-        <v>0.04</v>
-      </c>
-      <c r="G11">
-        <v>0.04</v>
-      </c>
-      <c r="H11">
-        <v>0.04</v>
-      </c>
-      <c r="I11">
-        <v>0.04</v>
-      </c>
-      <c r="J11">
-        <v>0.04</v>
-      </c>
-      <c r="K11">
-        <v>0.04</v>
-      </c>
-      <c r="L11">
-        <v>0.04</v>
-      </c>
-      <c r="M11">
-        <v>0.04</v>
-      </c>
-      <c r="N11">
-        <v>0.04</v>
-      </c>
-      <c r="O11">
-        <v>0.04</v>
-      </c>
-      <c r="P11">
-        <v>0.04</v>
-      </c>
-      <c r="Q11">
-        <v>0.04</v>
-      </c>
-      <c r="R11">
-        <v>0.04</v>
-      </c>
-      <c r="S11">
-        <v>4</v>
-      </c>
-      <c r="T11">
-        <v>4.48</v>
-      </c>
-      <c r="U11">
-        <v>4.92</v>
-      </c>
-      <c r="V11">
-        <v>5.6</v>
-      </c>
-      <c r="W11">
-        <v>5.93</v>
+        <v>101</v>
+      </c>
+      <c r="D11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" t="s">
+        <v>191</v>
+      </c>
+      <c r="I11" t="s">
+        <v>205</v>
+      </c>
+      <c r="J11" t="s">
+        <v>219</v>
+      </c>
+      <c r="K11" t="s">
+        <v>233</v>
+      </c>
+      <c r="L11" t="s">
+        <v>246</v>
+      </c>
+      <c r="M11" t="s">
+        <v>259</v>
+      </c>
+      <c r="N11" t="s">
+        <v>272</v>
+      </c>
+      <c r="O11" t="s">
+        <v>286</v>
+      </c>
+      <c r="P11" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>313</v>
+      </c>
+      <c r="R11" t="s">
+        <v>325</v>
+      </c>
+      <c r="S11" t="s">
+        <v>338</v>
+      </c>
+      <c r="T11" t="s">
+        <v>351</v>
+      </c>
+      <c r="U11" t="s">
+        <v>361</v>
+      </c>
+      <c r="V11" t="s">
+        <v>372</v>
+      </c>
+      <c r="W11" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="12" spans="1:23">
       <c r="A12" s="1" t="s">
         <v>32</v>
       </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
       <c r="C12" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12">
-        <v>495</v>
-      </c>
-      <c r="E12">
-        <v>1080</v>
-      </c>
-      <c r="F12">
-        <v>1399</v>
-      </c>
-      <c r="G12">
-        <v>438</v>
-      </c>
-      <c r="H12">
-        <v>1443</v>
-      </c>
-      <c r="I12">
-        <v>1069</v>
-      </c>
-      <c r="J12">
-        <v>1942</v>
-      </c>
-      <c r="K12">
+        <v>101</v>
+      </c>
+      <c r="D12" t="s">
+        <v>137</v>
+      </c>
+      <c r="E12" t="s">
+        <v>151</v>
+      </c>
+      <c r="F12" t="s">
+        <v>164</v>
+      </c>
+      <c r="G12" t="s">
+        <v>178</v>
+      </c>
+      <c r="H12" t="s">
         <v>192</v>
       </c>
-      <c r="L12">
-        <v>1685</v>
-      </c>
-      <c r="M12">
-        <v>2423</v>
-      </c>
-      <c r="N12">
-        <v>3565</v>
-      </c>
-      <c r="O12">
-        <v>3615</v>
-      </c>
-      <c r="P12">
-        <v>3242</v>
-      </c>
-      <c r="Q12">
-        <v>8435</v>
-      </c>
-      <c r="R12">
-        <v>9256</v>
-      </c>
-      <c r="S12">
-        <v>6037</v>
-      </c>
-      <c r="T12">
-        <v>7361</v>
-      </c>
-      <c r="U12">
-        <v>10240</v>
-      </c>
-      <c r="V12">
-        <v>8957</v>
-      </c>
-      <c r="W12">
-        <v>7437</v>
+      <c r="I12" t="s">
+        <v>206</v>
+      </c>
+      <c r="J12" t="s">
+        <v>220</v>
+      </c>
+      <c r="K12" t="s">
+        <v>234</v>
+      </c>
+      <c r="L12" t="s">
+        <v>247</v>
+      </c>
+      <c r="M12" t="s">
+        <v>260</v>
+      </c>
+      <c r="N12" t="s">
+        <v>273</v>
+      </c>
+      <c r="O12" t="s">
+        <v>242</v>
+      </c>
+      <c r="P12" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>314</v>
+      </c>
+      <c r="R12" t="s">
+        <v>326</v>
+      </c>
+      <c r="S12" t="s">
+        <v>339</v>
+      </c>
+      <c r="T12" t="s">
+        <v>280</v>
+      </c>
+      <c r="U12" t="s">
+        <v>362</v>
+      </c>
+      <c r="V12" t="s">
+        <v>373</v>
+      </c>
+      <c r="W12" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="13" spans="1:23">
       <c r="A13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B13" t="s">
-        <v>61</v>
-      </c>
       <c r="C13" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F13" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G13" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="H13" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="I13" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="J13" t="s">
-        <v>202</v>
+        <v>133</v>
       </c>
       <c r="K13" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s">
-        <v>231</v>
+        <v>133</v>
       </c>
       <c r="M13" t="s">
-        <v>245</v>
+        <v>133</v>
       </c>
       <c r="N13" t="s">
-        <v>259</v>
+        <v>133</v>
       </c>
       <c r="O13" t="s">
-        <v>273</v>
+        <v>133</v>
       </c>
       <c r="P13" t="s">
-        <v>288</v>
+        <v>133</v>
       </c>
       <c r="Q13" t="s">
-        <v>303</v>
+        <v>133</v>
       </c>
       <c r="R13" t="s">
-        <v>316</v>
+        <v>133</v>
       </c>
       <c r="S13" t="s">
-        <v>330</v>
+        <v>133</v>
       </c>
       <c r="T13" t="s">
-        <v>222</v>
+        <v>133</v>
       </c>
       <c r="U13" t="s">
-        <v>355</v>
+        <v>133</v>
       </c>
       <c r="V13" t="s">
-        <v>367</v>
+        <v>133</v>
       </c>
       <c r="W13" t="s">
-        <v>372</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:23">
@@ -2468,141 +2501,138 @@
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="F14" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G14" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="H14" t="s">
-        <v>173</v>
+        <v>137</v>
       </c>
       <c r="I14" t="s">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="J14" t="s">
-        <v>203</v>
+        <v>137</v>
       </c>
       <c r="K14" t="s">
-        <v>217</v>
+        <v>137</v>
       </c>
       <c r="L14" t="s">
-        <v>232</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s">
-        <v>246</v>
+        <v>137</v>
       </c>
       <c r="N14" t="s">
-        <v>260</v>
+        <v>137</v>
       </c>
       <c r="O14" t="s">
-        <v>274</v>
+        <v>137</v>
       </c>
       <c r="P14" t="s">
-        <v>289</v>
+        <v>137</v>
       </c>
       <c r="Q14" t="s">
-        <v>304</v>
+        <v>137</v>
       </c>
       <c r="R14" t="s">
-        <v>317</v>
+        <v>137</v>
       </c>
       <c r="S14" t="s">
-        <v>331</v>
+        <v>137</v>
       </c>
       <c r="T14" t="s">
-        <v>343</v>
+        <v>137</v>
       </c>
       <c r="U14" t="s">
-        <v>356</v>
+        <v>137</v>
       </c>
       <c r="V14" t="s">
-        <v>368</v>
+        <v>137</v>
       </c>
       <c r="W14" t="s">
-        <v>380</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:23">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B15" t="s">
-        <v>63</v>
-      </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F15" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="G15" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="H15" t="s">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="I15" t="s">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="J15" t="s">
-        <v>204</v>
+        <v>133</v>
       </c>
       <c r="K15" t="s">
-        <v>218</v>
+        <v>133</v>
       </c>
       <c r="L15" t="s">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="M15" t="s">
-        <v>247</v>
+        <v>133</v>
       </c>
       <c r="N15" t="s">
-        <v>261</v>
+        <v>133</v>
       </c>
       <c r="O15" t="s">
-        <v>275</v>
+        <v>133</v>
       </c>
       <c r="P15" t="s">
-        <v>290</v>
+        <v>133</v>
       </c>
       <c r="Q15" t="s">
-        <v>305</v>
+        <v>133</v>
       </c>
       <c r="R15" t="s">
-        <v>318</v>
+        <v>133</v>
       </c>
       <c r="S15" t="s">
-        <v>332</v>
+        <v>133</v>
       </c>
       <c r="T15" t="s">
-        <v>344</v>
+        <v>133</v>
       </c>
       <c r="U15" t="s">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="V15" t="s">
-        <v>318</v>
+        <v>133</v>
       </c>
       <c r="W15" t="s">
-        <v>381</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16" spans="1:23">
@@ -2610,70 +2640,70 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F16" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G16" t="s">
-        <v>160</v>
+        <v>137</v>
       </c>
       <c r="H16" t="s">
-        <v>175</v>
+        <v>137</v>
       </c>
       <c r="I16" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="J16" t="s">
-        <v>205</v>
+        <v>137</v>
       </c>
       <c r="K16" t="s">
-        <v>219</v>
+        <v>137</v>
       </c>
       <c r="L16" t="s">
-        <v>233</v>
+        <v>137</v>
       </c>
       <c r="M16" t="s">
-        <v>248</v>
+        <v>137</v>
       </c>
       <c r="N16" t="s">
-        <v>262</v>
+        <v>137</v>
       </c>
       <c r="O16" t="s">
-        <v>276</v>
+        <v>137</v>
       </c>
       <c r="P16" t="s">
-        <v>291</v>
+        <v>137</v>
       </c>
       <c r="Q16" t="s">
         <v>137</v>
       </c>
       <c r="R16" t="s">
-        <v>319</v>
+        <v>137</v>
       </c>
       <c r="S16" t="s">
-        <v>333</v>
+        <v>137</v>
       </c>
       <c r="T16" t="s">
-        <v>345</v>
+        <v>137</v>
       </c>
       <c r="U16" t="s">
-        <v>357</v>
+        <v>137</v>
       </c>
       <c r="V16" t="s">
-        <v>369</v>
+        <v>137</v>
       </c>
       <c r="W16" t="s">
-        <v>382</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -2681,212 +2711,206 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D17" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="E17" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="F17" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="G17" t="s">
-        <v>161</v>
+        <v>137</v>
       </c>
       <c r="H17" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="I17" t="s">
-        <v>191</v>
+        <v>137</v>
       </c>
       <c r="J17" t="s">
-        <v>206</v>
+        <v>137</v>
       </c>
       <c r="K17" t="s">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="L17" t="s">
-        <v>234</v>
+        <v>137</v>
       </c>
       <c r="M17" t="s">
-        <v>249</v>
+        <v>137</v>
       </c>
       <c r="N17" t="s">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="O17" t="s">
-        <v>277</v>
+        <v>137</v>
       </c>
       <c r="P17" t="s">
-        <v>292</v>
+        <v>137</v>
       </c>
       <c r="Q17" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="R17" t="s">
-        <v>320</v>
+        <v>137</v>
       </c>
       <c r="S17" t="s">
-        <v>334</v>
+        <v>137</v>
       </c>
       <c r="T17" t="s">
-        <v>346</v>
+        <v>137</v>
       </c>
       <c r="U17" t="s">
-        <v>358</v>
+        <v>137</v>
       </c>
       <c r="V17" t="s">
-        <v>370</v>
+        <v>137</v>
       </c>
       <c r="W17" t="s">
-        <v>383</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:23">
       <c r="A18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B18" t="s">
-        <v>65</v>
-      </c>
       <c r="C18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" t="s">
-        <v>132</v>
-      </c>
-      <c r="F18" t="s">
-        <v>147</v>
-      </c>
-      <c r="G18" t="s">
-        <v>162</v>
-      </c>
-      <c r="H18" t="s">
-        <v>177</v>
-      </c>
-      <c r="I18" t="s">
-        <v>192</v>
-      </c>
-      <c r="J18" t="s">
-        <v>207</v>
-      </c>
-      <c r="K18" t="s">
-        <v>221</v>
-      </c>
-      <c r="L18" t="s">
-        <v>235</v>
-      </c>
-      <c r="M18" t="s">
-        <v>235</v>
-      </c>
-      <c r="N18" t="s">
-        <v>264</v>
-      </c>
-      <c r="O18" t="s">
-        <v>278</v>
-      </c>
-      <c r="P18" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>306</v>
-      </c>
-      <c r="R18" t="s">
-        <v>221</v>
-      </c>
-      <c r="S18" t="s">
-        <v>159</v>
-      </c>
-      <c r="T18" t="s">
-        <v>344</v>
-      </c>
-      <c r="U18" t="s">
-        <v>332</v>
-      </c>
-      <c r="V18" t="s">
-        <v>371</v>
-      </c>
-      <c r="W18" t="s">
-        <v>384</v>
+        <v>107</v>
+      </c>
+      <c r="D18">
+        <v>0.033</v>
+      </c>
+      <c r="E18">
+        <v>0.038</v>
+      </c>
+      <c r="F18">
+        <v>0.04</v>
+      </c>
+      <c r="G18">
+        <v>0.04</v>
+      </c>
+      <c r="H18">
+        <v>0.04</v>
+      </c>
+      <c r="I18">
+        <v>0.04</v>
+      </c>
+      <c r="J18">
+        <v>0.04</v>
+      </c>
+      <c r="K18">
+        <v>0.04</v>
+      </c>
+      <c r="L18">
+        <v>0.04</v>
+      </c>
+      <c r="M18">
+        <v>0.04</v>
+      </c>
+      <c r="N18">
+        <v>0.04</v>
+      </c>
+      <c r="O18">
+        <v>0.04</v>
+      </c>
+      <c r="P18">
+        <v>0.04</v>
+      </c>
+      <c r="Q18">
+        <v>0.04</v>
+      </c>
+      <c r="R18">
+        <v>0.04</v>
+      </c>
+      <c r="S18">
+        <v>4</v>
+      </c>
+      <c r="T18">
+        <v>4.48</v>
+      </c>
+      <c r="U18">
+        <v>4.92</v>
+      </c>
+      <c r="V18">
+        <v>5.6</v>
+      </c>
+      <c r="W18">
+        <v>5.93</v>
       </c>
     </row>
     <row r="19" spans="1:23">
       <c r="A19" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B19" t="s">
-        <v>66</v>
-      </c>
       <c r="C19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" t="s">
-        <v>133</v>
-      </c>
-      <c r="F19" t="s">
-        <v>148</v>
-      </c>
-      <c r="G19" t="s">
-        <v>163</v>
-      </c>
-      <c r="H19" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" t="s">
-        <v>193</v>
-      </c>
-      <c r="J19" t="s">
-        <v>208</v>
-      </c>
-      <c r="K19" t="s">
-        <v>222</v>
-      </c>
-      <c r="L19" t="s">
-        <v>236</v>
-      </c>
-      <c r="M19" t="s">
-        <v>250</v>
-      </c>
-      <c r="N19" t="s">
-        <v>265</v>
-      </c>
-      <c r="O19" t="s">
-        <v>279</v>
-      </c>
-      <c r="P19" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>307</v>
-      </c>
-      <c r="R19" t="s">
-        <v>321</v>
-      </c>
-      <c r="S19" t="s">
-        <v>335</v>
-      </c>
-      <c r="T19" t="s">
-        <v>347</v>
-      </c>
-      <c r="U19" t="s">
-        <v>183</v>
-      </c>
-      <c r="V19" t="s">
-        <v>372</v>
-      </c>
-      <c r="W19" t="s">
-        <v>385</v>
+        <v>108</v>
+      </c>
+      <c r="D19">
+        <v>495</v>
+      </c>
+      <c r="E19">
+        <v>1080</v>
+      </c>
+      <c r="F19">
+        <v>1399</v>
+      </c>
+      <c r="G19">
+        <v>438</v>
+      </c>
+      <c r="H19">
+        <v>1443</v>
+      </c>
+      <c r="I19">
+        <v>1069</v>
+      </c>
+      <c r="J19">
+        <v>1942</v>
+      </c>
+      <c r="K19">
+        <v>192</v>
+      </c>
+      <c r="L19">
+        <v>1685</v>
+      </c>
+      <c r="M19">
+        <v>2423</v>
+      </c>
+      <c r="N19">
+        <v>3565</v>
+      </c>
+      <c r="O19">
+        <v>3615</v>
+      </c>
+      <c r="P19">
+        <v>3242</v>
+      </c>
+      <c r="Q19">
+        <v>8435</v>
+      </c>
+      <c r="R19">
+        <v>9256</v>
+      </c>
+      <c r="S19">
+        <v>6037</v>
+      </c>
+      <c r="T19">
+        <v>7361</v>
+      </c>
+      <c r="U19">
+        <v>10240</v>
+      </c>
+      <c r="V19">
+        <v>8957</v>
+      </c>
+      <c r="W19">
+        <v>7437</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -2894,70 +2918,70 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E20" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="F20" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="G20" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="H20" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="I20" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="J20" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="K20" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="L20" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="M20" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="N20" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="O20" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="P20" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="Q20" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="R20" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="S20" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="T20" t="s">
-        <v>348</v>
+        <v>240</v>
       </c>
       <c r="U20" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="V20" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="W20" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -2965,10 +2989,70 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" t="s">
+        <v>153</v>
+      </c>
+      <c r="F21" t="s">
+        <v>166</v>
+      </c>
+      <c r="G21" t="s">
+        <v>180</v>
+      </c>
+      <c r="H21" t="s">
+        <v>194</v>
+      </c>
+      <c r="I21" t="s">
+        <v>208</v>
+      </c>
+      <c r="J21" t="s">
+        <v>222</v>
+      </c>
+      <c r="K21" t="s">
+        <v>235</v>
+      </c>
+      <c r="L21" t="s">
+        <v>249</v>
+      </c>
+      <c r="M21" t="s">
+        <v>262</v>
+      </c>
+      <c r="N21" t="s">
+        <v>275</v>
+      </c>
+      <c r="O21" t="s">
+        <v>288</v>
+      </c>
+      <c r="P21" t="s">
+        <v>302</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>316</v>
+      </c>
+      <c r="R21" t="s">
+        <v>328</v>
+      </c>
+      <c r="S21" t="s">
+        <v>341</v>
+      </c>
+      <c r="T21" t="s">
+        <v>352</v>
+      </c>
+      <c r="U21" t="s">
+        <v>364</v>
+      </c>
+      <c r="V21" t="s">
+        <v>375</v>
+      </c>
+      <c r="W21" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -2976,70 +3060,70 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22">
-        <v>0</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>0</v>
-      </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>0</v>
-      </c>
-      <c r="Q22">
-        <v>0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>1.08</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
+        <v>110</v>
+      </c>
+      <c r="D22" t="s">
+        <v>140</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" t="s">
+        <v>167</v>
+      </c>
+      <c r="G22" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" t="s">
+        <v>195</v>
+      </c>
+      <c r="I22" t="s">
+        <v>209</v>
+      </c>
+      <c r="J22" t="s">
+        <v>223</v>
+      </c>
+      <c r="K22" t="s">
+        <v>236</v>
+      </c>
+      <c r="L22" t="s">
+        <v>226</v>
+      </c>
+      <c r="M22" t="s">
+        <v>263</v>
+      </c>
+      <c r="N22" t="s">
+        <v>276</v>
+      </c>
+      <c r="O22" t="s">
+        <v>289</v>
+      </c>
+      <c r="P22" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>317</v>
+      </c>
+      <c r="R22" t="s">
+        <v>329</v>
+      </c>
+      <c r="S22" t="s">
+        <v>342</v>
+      </c>
+      <c r="T22" t="s">
+        <v>353</v>
+      </c>
+      <c r="U22" t="s">
+        <v>226</v>
+      </c>
+      <c r="V22" t="s">
+        <v>329</v>
+      </c>
+      <c r="W22" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="23" spans="1:23">
@@ -3047,70 +3131,70 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23">
-        <v>12.79</v>
-      </c>
-      <c r="E23">
-        <v>13.88</v>
-      </c>
-      <c r="F23">
-        <v>16.05</v>
-      </c>
-      <c r="G23">
-        <v>7.46</v>
-      </c>
-      <c r="H23">
-        <v>7.88</v>
-      </c>
-      <c r="I23">
-        <v>9.15</v>
-      </c>
-      <c r="J23">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="K23">
-        <v>16.89</v>
-      </c>
-      <c r="L23">
-        <v>13.14</v>
-      </c>
-      <c r="M23">
-        <v>18.2</v>
-      </c>
-      <c r="N23">
-        <v>18.55</v>
-      </c>
-      <c r="O23">
-        <v>23.16</v>
-      </c>
-      <c r="P23">
-        <v>18.02</v>
-      </c>
-      <c r="Q23">
-        <v>15.22</v>
-      </c>
-      <c r="R23">
-        <v>9.07</v>
-      </c>
-      <c r="S23">
-        <v>14.58</v>
-      </c>
-      <c r="T23">
-        <v>15.48</v>
-      </c>
-      <c r="U23">
-        <v>17.22</v>
-      </c>
-      <c r="V23">
-        <v>22.78</v>
-      </c>
-      <c r="W23">
-        <v>11.95</v>
+        <v>111</v>
+      </c>
+      <c r="D23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" t="s">
+        <v>155</v>
+      </c>
+      <c r="F23" t="s">
+        <v>168</v>
+      </c>
+      <c r="G23" t="s">
+        <v>182</v>
+      </c>
+      <c r="H23" t="s">
+        <v>196</v>
+      </c>
+      <c r="I23" t="s">
+        <v>210</v>
+      </c>
+      <c r="J23" t="s">
+        <v>224</v>
+      </c>
+      <c r="K23" t="s">
+        <v>237</v>
+      </c>
+      <c r="L23" t="s">
+        <v>250</v>
+      </c>
+      <c r="M23" t="s">
+        <v>264</v>
+      </c>
+      <c r="N23" t="s">
+        <v>277</v>
+      </c>
+      <c r="O23" t="s">
+        <v>290</v>
+      </c>
+      <c r="P23" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>160</v>
+      </c>
+      <c r="R23" t="s">
+        <v>330</v>
+      </c>
+      <c r="S23" t="s">
+        <v>343</v>
+      </c>
+      <c r="T23" t="s">
+        <v>354</v>
+      </c>
+      <c r="U23" t="s">
+        <v>365</v>
+      </c>
+      <c r="V23" t="s">
+        <v>376</v>
+      </c>
+      <c r="W23" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="24" spans="1:23">
@@ -3118,70 +3202,70 @@
         <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24">
-        <v>0.89</v>
-      </c>
-      <c r="E24">
-        <v>0.86</v>
-      </c>
-      <c r="F24">
-        <v>0.25</v>
-      </c>
-      <c r="G24">
-        <v>0.53</v>
-      </c>
-      <c r="H24">
-        <v>0.48</v>
-      </c>
-      <c r="I24">
-        <v>0.53</v>
-      </c>
-      <c r="J24">
-        <v>0.53</v>
-      </c>
-      <c r="K24">
-        <v>0.77</v>
-      </c>
-      <c r="L24">
-        <v>0.79</v>
-      </c>
-      <c r="M24">
-        <v>1.01</v>
-      </c>
-      <c r="N24">
-        <v>0.87</v>
-      </c>
-      <c r="O24">
-        <v>1.23</v>
-      </c>
-      <c r="P24">
-        <v>0.96</v>
-      </c>
-      <c r="Q24">
-        <v>0.51</v>
-      </c>
-      <c r="R24">
-        <v>0.48</v>
-      </c>
-      <c r="S24">
-        <v>0.45</v>
-      </c>
-      <c r="T24">
-        <v>0.58</v>
-      </c>
-      <c r="U24">
-        <v>0.46</v>
-      </c>
-      <c r="V24">
-        <v>0.32</v>
-      </c>
-      <c r="W24">
-        <v>0.27</v>
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F24" t="s">
+        <v>169</v>
+      </c>
+      <c r="G24" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" t="s">
+        <v>197</v>
+      </c>
+      <c r="I24" t="s">
+        <v>211</v>
+      </c>
+      <c r="J24" t="s">
+        <v>225</v>
+      </c>
+      <c r="K24" t="s">
+        <v>238</v>
+      </c>
+      <c r="L24" t="s">
+        <v>251</v>
+      </c>
+      <c r="M24" t="s">
+        <v>265</v>
+      </c>
+      <c r="N24" t="s">
+        <v>278</v>
+      </c>
+      <c r="O24" t="s">
+        <v>291</v>
+      </c>
+      <c r="P24" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>154</v>
+      </c>
+      <c r="R24" t="s">
+        <v>331</v>
+      </c>
+      <c r="S24" t="s">
+        <v>344</v>
+      </c>
+      <c r="T24" t="s">
+        <v>355</v>
+      </c>
+      <c r="U24" t="s">
+        <v>366</v>
+      </c>
+      <c r="V24" t="s">
+        <v>377</v>
+      </c>
+      <c r="W24" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -3189,70 +3273,70 @@
         <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25">
-        <v>2.65</v>
-      </c>
-      <c r="E25">
-        <v>2.7</v>
-      </c>
-      <c r="F25">
-        <v>0.72</v>
-      </c>
-      <c r="G25">
-        <v>3.08</v>
-      </c>
-      <c r="H25">
-        <v>2.88</v>
-      </c>
-      <c r="I25">
-        <v>2.61</v>
-      </c>
-      <c r="J25">
-        <v>3.11</v>
-      </c>
-      <c r="K25">
-        <v>2.73</v>
-      </c>
-      <c r="L25">
-        <v>3.81</v>
-      </c>
-      <c r="M25">
-        <v>3.71</v>
-      </c>
-      <c r="N25">
-        <v>3.21</v>
-      </c>
-      <c r="O25">
-        <v>3.69</v>
-      </c>
-      <c r="P25">
-        <v>2.45</v>
-      </c>
-      <c r="Q25">
-        <v>3.3</v>
-      </c>
-      <c r="R25">
-        <v>5.44</v>
-      </c>
-      <c r="S25">
-        <v>3.46</v>
-      </c>
-      <c r="T25">
-        <v>4.49</v>
-      </c>
-      <c r="U25">
-        <v>3.48</v>
-      </c>
-      <c r="V25">
-        <v>2.23</v>
-      </c>
-      <c r="W25">
-        <v>3.97</v>
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
+        <v>143</v>
+      </c>
+      <c r="E25" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" t="s">
+        <v>170</v>
+      </c>
+      <c r="G25" t="s">
+        <v>184</v>
+      </c>
+      <c r="H25" t="s">
+        <v>198</v>
+      </c>
+      <c r="I25" t="s">
+        <v>212</v>
+      </c>
+      <c r="J25" t="s">
+        <v>226</v>
+      </c>
+      <c r="K25" t="s">
+        <v>239</v>
+      </c>
+      <c r="L25" t="s">
+        <v>252</v>
+      </c>
+      <c r="M25" t="s">
+        <v>252</v>
+      </c>
+      <c r="N25" t="s">
+        <v>279</v>
+      </c>
+      <c r="O25" t="s">
+        <v>292</v>
+      </c>
+      <c r="P25" t="s">
+        <v>306</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>318</v>
+      </c>
+      <c r="R25" t="s">
+        <v>239</v>
+      </c>
+      <c r="S25" t="s">
+        <v>181</v>
+      </c>
+      <c r="T25" t="s">
+        <v>353</v>
+      </c>
+      <c r="U25" t="s">
+        <v>342</v>
+      </c>
+      <c r="V25" t="s">
+        <v>378</v>
+      </c>
+      <c r="W25" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -3260,209 +3344,209 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26">
-        <v>23.84</v>
-      </c>
-      <c r="E26">
-        <v>24.56</v>
-      </c>
-      <c r="F26">
-        <v>7.000000000000001</v>
-      </c>
-      <c r="G26">
-        <v>28.9</v>
-      </c>
-      <c r="H26">
-        <v>21.21</v>
-      </c>
-      <c r="I26">
-        <v>17.21</v>
-      </c>
-      <c r="J26">
-        <v>18.27</v>
-      </c>
-      <c r="K26">
-        <v>14.52</v>
-      </c>
-      <c r="L26">
-        <v>19.7</v>
-      </c>
-      <c r="M26">
-        <v>18.36</v>
-      </c>
-      <c r="N26">
-        <v>14.5</v>
-      </c>
-      <c r="O26">
-        <v>16.31</v>
-      </c>
-      <c r="P26">
-        <v>9.629999999999999</v>
-      </c>
-      <c r="Q26">
-        <v>11.82</v>
-      </c>
-      <c r="R26">
-        <v>17.68</v>
-      </c>
-      <c r="S26">
-        <v>11.02</v>
-      </c>
-      <c r="T26">
-        <v>14.61</v>
-      </c>
-      <c r="U26">
-        <v>11.36</v>
-      </c>
-      <c r="V26">
-        <v>7.870000000000001</v>
-      </c>
-      <c r="W26">
-        <v>14.97</v>
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>144</v>
+      </c>
+      <c r="E26" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26" t="s">
+        <v>171</v>
+      </c>
+      <c r="G26" t="s">
+        <v>185</v>
+      </c>
+      <c r="H26" t="s">
+        <v>199</v>
+      </c>
+      <c r="I26" t="s">
+        <v>213</v>
+      </c>
+      <c r="J26" t="s">
+        <v>227</v>
+      </c>
+      <c r="K26" t="s">
+        <v>240</v>
+      </c>
+      <c r="L26" t="s">
+        <v>253</v>
+      </c>
+      <c r="M26" t="s">
+        <v>266</v>
+      </c>
+      <c r="N26" t="s">
+        <v>280</v>
+      </c>
+      <c r="O26" t="s">
+        <v>293</v>
+      </c>
+      <c r="P26" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>319</v>
+      </c>
+      <c r="R26" t="s">
+        <v>332</v>
+      </c>
+      <c r="S26" t="s">
+        <v>345</v>
+      </c>
+      <c r="T26" t="s">
+        <v>356</v>
+      </c>
+      <c r="U26" t="s">
+        <v>203</v>
+      </c>
+      <c r="V26" t="s">
+        <v>379</v>
+      </c>
+      <c r="W26" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="27" spans="1:23">
       <c r="A27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
       <c r="C27" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F27" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="G27" t="s">
-        <v>165</v>
+        <v>133</v>
       </c>
       <c r="H27" t="s">
-        <v>180</v>
+        <v>133</v>
       </c>
       <c r="I27" t="s">
-        <v>195</v>
+        <v>133</v>
       </c>
       <c r="J27" t="s">
-        <v>210</v>
+        <v>133</v>
       </c>
       <c r="K27" t="s">
-        <v>224</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s">
-        <v>238</v>
+        <v>133</v>
       </c>
       <c r="M27" t="s">
-        <v>252</v>
+        <v>133</v>
       </c>
       <c r="N27" t="s">
-        <v>267</v>
+        <v>133</v>
       </c>
       <c r="O27" t="s">
-        <v>281</v>
+        <v>133</v>
       </c>
       <c r="P27" t="s">
-        <v>296</v>
+        <v>133</v>
       </c>
       <c r="Q27" t="s">
-        <v>309</v>
+        <v>133</v>
       </c>
       <c r="R27" t="s">
-        <v>323</v>
+        <v>133</v>
       </c>
       <c r="S27" t="s">
-        <v>337</v>
+        <v>133</v>
       </c>
       <c r="T27" t="s">
-        <v>349</v>
+        <v>133</v>
       </c>
       <c r="U27" t="s">
-        <v>360</v>
+        <v>133</v>
       </c>
       <c r="V27" t="s">
-        <v>374</v>
+        <v>133</v>
       </c>
       <c r="W27" t="s">
-        <v>387</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28" spans="1:23">
       <c r="A28" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="B28" t="s">
+        <v>80</v>
+      </c>
       <c r="C28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28">
-        <v>11.68</v>
-      </c>
-      <c r="E28">
-        <v>8.789999999999999</v>
-      </c>
-      <c r="F28">
-        <v>11.25</v>
-      </c>
-      <c r="G28">
-        <v>12.03</v>
-      </c>
-      <c r="H28">
-        <v>10.9</v>
-      </c>
-      <c r="I28">
-        <v>5.34</v>
-      </c>
-      <c r="J28">
-        <v>3.79</v>
-      </c>
-      <c r="K28">
-        <v>6.49</v>
-      </c>
-      <c r="L28">
-        <v>5.44</v>
-      </c>
-      <c r="M28">
-        <v>3.67</v>
-      </c>
-      <c r="N28">
-        <v>4.17</v>
-      </c>
-      <c r="O28">
-        <v>4.35</v>
-      </c>
-      <c r="P28">
-        <v>7.96</v>
-      </c>
-      <c r="Q28">
-        <v>6.5</v>
-      </c>
-      <c r="R28">
-        <v>5.12</v>
-      </c>
-      <c r="S28">
-        <v>5.64</v>
-      </c>
-      <c r="T28">
-        <v>6.38</v>
-      </c>
-      <c r="U28">
-        <v>5.35</v>
-      </c>
-      <c r="V28">
-        <v>5.39</v>
-      </c>
-      <c r="W28">
-        <v>4.08</v>
+        <v>116</v>
+      </c>
+      <c r="D28" t="s">
+        <v>145</v>
+      </c>
+      <c r="E28" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" t="s">
+        <v>172</v>
+      </c>
+      <c r="G28" t="s">
+        <v>186</v>
+      </c>
+      <c r="H28" t="s">
+        <v>200</v>
+      </c>
+      <c r="I28" t="s">
+        <v>214</v>
+      </c>
+      <c r="J28" t="s">
+        <v>228</v>
+      </c>
+      <c r="K28" t="s">
+        <v>241</v>
+      </c>
+      <c r="L28" t="s">
+        <v>254</v>
+      </c>
+      <c r="M28" t="s">
+        <v>267</v>
+      </c>
+      <c r="N28" t="s">
+        <v>281</v>
+      </c>
+      <c r="O28" t="s">
+        <v>294</v>
+      </c>
+      <c r="P28" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>320</v>
+      </c>
+      <c r="R28" t="s">
+        <v>333</v>
+      </c>
+      <c r="S28" t="s">
+        <v>346</v>
+      </c>
+      <c r="T28" t="s">
+        <v>357</v>
+      </c>
+      <c r="U28" t="s">
+        <v>367</v>
+      </c>
+      <c r="V28" t="s">
+        <v>380</v>
+      </c>
+      <c r="W28" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="29" spans="1:23">
@@ -3470,70 +3554,10 @@
         <v>49</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" t="s">
-        <v>112</v>
-      </c>
-      <c r="E29" t="s">
-        <v>136</v>
-      </c>
-      <c r="F29" t="s">
-        <v>151</v>
-      </c>
-      <c r="G29" t="s">
-        <v>166</v>
-      </c>
-      <c r="H29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I29" t="s">
-        <v>196</v>
-      </c>
-      <c r="J29" t="s">
-        <v>211</v>
-      </c>
-      <c r="K29" t="s">
-        <v>225</v>
-      </c>
-      <c r="L29" t="s">
-        <v>239</v>
-      </c>
-      <c r="M29" t="s">
-        <v>253</v>
-      </c>
-      <c r="N29" t="s">
-        <v>268</v>
-      </c>
-      <c r="O29" t="s">
-        <v>282</v>
-      </c>
-      <c r="P29" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>310</v>
-      </c>
-      <c r="R29" t="s">
-        <v>324</v>
-      </c>
-      <c r="S29" t="s">
-        <v>338</v>
-      </c>
-      <c r="T29" t="s">
-        <v>350</v>
-      </c>
-      <c r="U29" t="s">
-        <v>361</v>
-      </c>
-      <c r="V29" t="s">
-        <v>292</v>
-      </c>
-      <c r="W29" t="s">
-        <v>388</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="1:23">
@@ -3541,250 +3565,283 @@
         <v>50</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30">
-        <v>14.616</v>
-      </c>
-      <c r="E30">
-        <v>16.982</v>
-      </c>
-      <c r="F30">
-        <v>13.253</v>
-      </c>
-      <c r="G30">
-        <v>19.7</v>
-      </c>
-      <c r="H30">
-        <v>24.441</v>
-      </c>
-      <c r="I30">
-        <v>27.997</v>
-      </c>
-      <c r="J30">
-        <v>34.178</v>
-      </c>
-      <c r="K30">
-        <v>38.352</v>
-      </c>
-      <c r="L30">
-        <v>41.554</v>
-      </c>
-      <c r="M30">
-        <v>46.912</v>
-      </c>
-      <c r="N30">
-        <v>53.424</v>
-      </c>
-      <c r="O30">
-        <v>56.2</v>
-      </c>
-      <c r="P30">
-        <v>107.707</v>
-      </c>
-      <c r="Q30">
-        <v>121.703</v>
-      </c>
-      <c r="R30">
-        <v>141.841</v>
-      </c>
-      <c r="S30">
-        <v>145.881</v>
-      </c>
-      <c r="T30">
-        <v>149.577</v>
-      </c>
-      <c r="U30">
-        <v>158.025</v>
-      </c>
-      <c r="V30">
-        <v>149.871</v>
-      </c>
-      <c r="W30">
-        <v>156.531</v>
+        <v>118</v>
+      </c>
+      <c r="D30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" t="s">
+        <v>133</v>
+      </c>
+      <c r="F30" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30" t="s">
+        <v>133</v>
+      </c>
+      <c r="H30" t="s">
+        <v>133</v>
+      </c>
+      <c r="I30" t="s">
+        <v>133</v>
+      </c>
+      <c r="J30" t="s">
+        <v>133</v>
+      </c>
+      <c r="K30" t="s">
+        <v>133</v>
+      </c>
+      <c r="L30" t="s">
+        <v>133</v>
+      </c>
+      <c r="M30" t="s">
+        <v>133</v>
+      </c>
+      <c r="N30" t="s">
+        <v>133</v>
+      </c>
+      <c r="O30" t="s">
+        <v>133</v>
+      </c>
+      <c r="P30" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>133</v>
+      </c>
+      <c r="R30" t="s">
+        <v>133</v>
+      </c>
+      <c r="S30" t="s">
+        <v>133</v>
+      </c>
+      <c r="T30" t="s">
+        <v>133</v>
+      </c>
+      <c r="U30" t="s">
+        <v>133</v>
+      </c>
+      <c r="V30" t="s">
+        <v>133</v>
+      </c>
+      <c r="W30" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="31" spans="1:23">
       <c r="A31" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="B31" t="s">
+        <v>83</v>
+      </c>
       <c r="C31" t="s">
-        <v>103</v>
-      </c>
-      <c r="D31">
-        <v>5</v>
-      </c>
-      <c r="E31">
-        <v>7</v>
-      </c>
-      <c r="F31">
-        <v>5</v>
-      </c>
-      <c r="G31">
-        <v>5</v>
-      </c>
-      <c r="H31">
-        <v>6</v>
-      </c>
-      <c r="I31">
-        <v>5</v>
-      </c>
-      <c r="J31">
-        <v>7</v>
-      </c>
-      <c r="K31">
-        <v>6</v>
-      </c>
-      <c r="L31">
-        <v>8</v>
-      </c>
-      <c r="M31">
-        <v>7</v>
-      </c>
-      <c r="N31">
-        <v>7</v>
-      </c>
-      <c r="O31">
-        <v>7</v>
-      </c>
-      <c r="P31">
-        <v>7</v>
-      </c>
-      <c r="Q31">
-        <v>6</v>
-      </c>
-      <c r="R31">
-        <v>9</v>
-      </c>
-      <c r="S31">
-        <v>5</v>
-      </c>
-      <c r="T31">
-        <v>9</v>
-      </c>
-      <c r="U31">
-        <v>5</v>
-      </c>
-      <c r="V31">
-        <v>6</v>
-      </c>
-      <c r="W31">
-        <v>7</v>
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" t="s">
+        <v>133</v>
+      </c>
+      <c r="F31" t="s">
+        <v>133</v>
+      </c>
+      <c r="G31" t="s">
+        <v>133</v>
+      </c>
+      <c r="H31" t="s">
+        <v>133</v>
+      </c>
+      <c r="I31" t="s">
+        <v>133</v>
+      </c>
+      <c r="J31" t="s">
+        <v>133</v>
+      </c>
+      <c r="K31" t="s">
+        <v>133</v>
+      </c>
+      <c r="L31" t="s">
+        <v>133</v>
+      </c>
+      <c r="M31" t="s">
+        <v>133</v>
+      </c>
+      <c r="N31" t="s">
+        <v>133</v>
+      </c>
+      <c r="O31" t="s">
+        <v>133</v>
+      </c>
+      <c r="P31" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>133</v>
+      </c>
+      <c r="R31" t="s">
+        <v>133</v>
+      </c>
+      <c r="S31" t="s">
+        <v>133</v>
+      </c>
+      <c r="T31" t="s">
+        <v>133</v>
+      </c>
+      <c r="U31" t="s">
+        <v>133</v>
+      </c>
+      <c r="V31" t="s">
+        <v>133</v>
+      </c>
+      <c r="W31" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:23">
       <c r="A32" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
       <c r="C32" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="D32">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="H32">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="K32">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q32">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>6.07</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>6.83</v>
+        <v>1.08</v>
       </c>
       <c r="V32">
-        <v>6.46</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>7.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:23">
       <c r="A33" s="1" t="s">
         <v>53</v>
       </c>
+      <c r="B33" t="s">
+        <v>85</v>
+      </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D33">
-        <v>36.48</v>
+        <v>12.79</v>
       </c>
       <c r="E33">
-        <v>44.4</v>
+        <v>13.88</v>
       </c>
       <c r="F33">
-        <v>18.58</v>
+        <v>16.05</v>
       </c>
       <c r="G33">
-        <v>118.42</v>
+        <v>7.46</v>
       </c>
       <c r="H33">
-        <v>67.80000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="I33">
-        <v>37.34</v>
+        <v>9.15</v>
       </c>
       <c r="J33">
-        <v>45.28</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="K33">
-        <v>46.53</v>
+        <v>16.89</v>
       </c>
       <c r="L33">
-        <v>54.51000000000001</v>
+        <v>13.14</v>
       </c>
       <c r="M33">
-        <v>43.97</v>
+        <v>18.2</v>
       </c>
       <c r="N33">
-        <v>29.25</v>
+        <v>18.55</v>
       </c>
       <c r="O33">
-        <v>30.81</v>
+        <v>23.16</v>
+      </c>
+      <c r="P33">
+        <v>18.02</v>
+      </c>
+      <c r="Q33">
+        <v>15.22</v>
+      </c>
+      <c r="R33">
+        <v>9.07</v>
+      </c>
+      <c r="S33">
+        <v>14.58</v>
+      </c>
+      <c r="T33">
+        <v>15.48</v>
+      </c>
+      <c r="U33">
+        <v>17.22</v>
+      </c>
+      <c r="V33">
+        <v>22.78</v>
+      </c>
+      <c r="W33">
+        <v>11.95</v>
       </c>
     </row>
     <row r="34" spans="1:23">
@@ -3792,138 +3849,141 @@
         <v>54</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>106</v>
-      </c>
-      <c r="D34" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" t="s">
-        <v>113</v>
-      </c>
-      <c r="F34" t="s">
-        <v>113</v>
-      </c>
-      <c r="G34" t="s">
-        <v>113</v>
-      </c>
-      <c r="H34" t="s">
-        <v>113</v>
-      </c>
-      <c r="I34" t="s">
-        <v>113</v>
-      </c>
-      <c r="J34" t="s">
-        <v>113</v>
-      </c>
-      <c r="K34" t="s">
-        <v>113</v>
-      </c>
-      <c r="L34" t="s">
-        <v>113</v>
-      </c>
-      <c r="M34" t="s">
-        <v>113</v>
-      </c>
-      <c r="N34" t="s">
-        <v>113</v>
-      </c>
-      <c r="O34" t="s">
-        <v>113</v>
-      </c>
-      <c r="P34" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>113</v>
-      </c>
-      <c r="R34" t="s">
-        <v>113</v>
-      </c>
-      <c r="S34" t="s">
-        <v>113</v>
-      </c>
-      <c r="T34" t="s">
-        <v>113</v>
-      </c>
-      <c r="U34" t="s">
-        <v>113</v>
-      </c>
-      <c r="V34" t="s">
-        <v>113</v>
-      </c>
-      <c r="W34" t="s">
-        <v>113</v>
+        <v>122</v>
+      </c>
+      <c r="D34">
+        <v>0.89</v>
+      </c>
+      <c r="E34">
+        <v>0.86</v>
+      </c>
+      <c r="F34">
+        <v>0.25</v>
+      </c>
+      <c r="G34">
+        <v>0.53</v>
+      </c>
+      <c r="H34">
+        <v>0.48</v>
+      </c>
+      <c r="I34">
+        <v>0.53</v>
+      </c>
+      <c r="J34">
+        <v>0.53</v>
+      </c>
+      <c r="K34">
+        <v>0.77</v>
+      </c>
+      <c r="L34">
+        <v>0.79</v>
+      </c>
+      <c r="M34">
+        <v>1.01</v>
+      </c>
+      <c r="N34">
+        <v>0.87</v>
+      </c>
+      <c r="O34">
+        <v>1.23</v>
+      </c>
+      <c r="P34">
+        <v>0.96</v>
+      </c>
+      <c r="Q34">
+        <v>0.51</v>
+      </c>
+      <c r="R34">
+        <v>0.48</v>
+      </c>
+      <c r="S34">
+        <v>0.45</v>
+      </c>
+      <c r="T34">
+        <v>0.58</v>
+      </c>
+      <c r="U34">
+        <v>0.46</v>
+      </c>
+      <c r="V34">
+        <v>0.32</v>
+      </c>
+      <c r="W34">
+        <v>0.27</v>
       </c>
     </row>
     <row r="35" spans="1:23">
       <c r="A35" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="B35" t="s">
+        <v>87</v>
+      </c>
       <c r="C35" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35">
-        <v>0.102</v>
-      </c>
-      <c r="E35">
-        <v>0.119</v>
-      </c>
-      <c r="F35">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="G35">
-        <v>0.126</v>
-      </c>
-      <c r="H35">
-        <v>0.145</v>
-      </c>
-      <c r="I35">
-        <v>0.158</v>
-      </c>
-      <c r="J35">
-        <v>0.182</v>
-      </c>
-      <c r="K35">
-        <v>0.194</v>
-      </c>
-      <c r="L35">
-        <v>0.193</v>
-      </c>
-      <c r="M35">
-        <v>0.211</v>
-      </c>
-      <c r="N35">
-        <v>0.231</v>
-      </c>
-      <c r="O35">
-        <v>0.222</v>
-      </c>
-      <c r="P35">
-        <v>0.268</v>
-      </c>
-      <c r="Q35">
-        <v>0.291</v>
-      </c>
-      <c r="R35">
-        <v>0.324</v>
-      </c>
-      <c r="S35">
-        <v>0.304</v>
-      </c>
-      <c r="T35">
-        <v>0.31</v>
-      </c>
-      <c r="U35">
-        <v>0.303</v>
-      </c>
-      <c r="V35">
-        <v>0.263</v>
-      </c>
-      <c r="W35">
-        <v>0.265</v>
+        <v>118</v>
+      </c>
+      <c r="D35" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" t="s">
+        <v>133</v>
+      </c>
+      <c r="F35" t="s">
+        <v>133</v>
+      </c>
+      <c r="G35" t="s">
+        <v>133</v>
+      </c>
+      <c r="H35" t="s">
+        <v>133</v>
+      </c>
+      <c r="I35" t="s">
+        <v>133</v>
+      </c>
+      <c r="J35" t="s">
+        <v>133</v>
+      </c>
+      <c r="K35" t="s">
+        <v>133</v>
+      </c>
+      <c r="L35" t="s">
+        <v>133</v>
+      </c>
+      <c r="M35" t="s">
+        <v>133</v>
+      </c>
+      <c r="N35" t="s">
+        <v>133</v>
+      </c>
+      <c r="O35" t="s">
+        <v>133</v>
+      </c>
+      <c r="P35" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>133</v>
+      </c>
+      <c r="R35" t="s">
+        <v>133</v>
+      </c>
+      <c r="S35" t="s">
+        <v>133</v>
+      </c>
+      <c r="T35" t="s">
+        <v>133</v>
+      </c>
+      <c r="U35" t="s">
+        <v>133</v>
+      </c>
+      <c r="V35" t="s">
+        <v>133</v>
+      </c>
+      <c r="W35" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:23">
@@ -3931,70 +3991,697 @@
         <v>56</v>
       </c>
       <c r="B36" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36" t="s">
-        <v>113</v>
-      </c>
-      <c r="E36" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" t="s">
-        <v>113</v>
-      </c>
-      <c r="G36" t="s">
-        <v>113</v>
-      </c>
-      <c r="H36" t="s">
-        <v>113</v>
-      </c>
-      <c r="I36" t="s">
-        <v>113</v>
-      </c>
-      <c r="J36" t="s">
-        <v>113</v>
-      </c>
-      <c r="K36" t="s">
-        <v>113</v>
-      </c>
-      <c r="L36" t="s">
-        <v>113</v>
-      </c>
-      <c r="M36" t="s">
-        <v>113</v>
-      </c>
-      <c r="N36" t="s">
-        <v>113</v>
-      </c>
-      <c r="O36" t="s">
-        <v>113</v>
-      </c>
-      <c r="P36" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>113</v>
-      </c>
-      <c r="R36" t="s">
-        <v>113</v>
-      </c>
-      <c r="S36" t="s">
-        <v>113</v>
-      </c>
-      <c r="T36" t="s">
-        <v>113</v>
-      </c>
-      <c r="U36" t="s">
-        <v>113</v>
-      </c>
-      <c r="V36" t="s">
-        <v>113</v>
-      </c>
-      <c r="W36" t="s">
-        <v>113</v>
+        <v>123</v>
+      </c>
+      <c r="D36">
+        <v>2.65</v>
+      </c>
+      <c r="E36">
+        <v>2.7</v>
+      </c>
+      <c r="F36">
+        <v>0.72</v>
+      </c>
+      <c r="G36">
+        <v>3.08</v>
+      </c>
+      <c r="H36">
+        <v>2.88</v>
+      </c>
+      <c r="I36">
+        <v>2.61</v>
+      </c>
+      <c r="J36">
+        <v>3.11</v>
+      </c>
+      <c r="K36">
+        <v>2.73</v>
+      </c>
+      <c r="L36">
+        <v>3.81</v>
+      </c>
+      <c r="M36">
+        <v>3.71</v>
+      </c>
+      <c r="N36">
+        <v>3.21</v>
+      </c>
+      <c r="O36">
+        <v>3.69</v>
+      </c>
+      <c r="P36">
+        <v>2.45</v>
+      </c>
+      <c r="Q36">
+        <v>3.3</v>
+      </c>
+      <c r="R36">
+        <v>5.44</v>
+      </c>
+      <c r="S36">
+        <v>3.46</v>
+      </c>
+      <c r="T36">
+        <v>4.49</v>
+      </c>
+      <c r="U36">
+        <v>3.48</v>
+      </c>
+      <c r="V36">
+        <v>2.23</v>
+      </c>
+      <c r="W36">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37">
+        <v>23.84</v>
+      </c>
+      <c r="E37">
+        <v>24.56</v>
+      </c>
+      <c r="F37">
+        <v>7.000000000000001</v>
+      </c>
+      <c r="G37">
+        <v>28.9</v>
+      </c>
+      <c r="H37">
+        <v>21.21</v>
+      </c>
+      <c r="I37">
+        <v>17.21</v>
+      </c>
+      <c r="J37">
+        <v>18.27</v>
+      </c>
+      <c r="K37">
+        <v>14.52</v>
+      </c>
+      <c r="L37">
+        <v>19.7</v>
+      </c>
+      <c r="M37">
+        <v>18.36</v>
+      </c>
+      <c r="N37">
+        <v>14.5</v>
+      </c>
+      <c r="O37">
+        <v>16.31</v>
+      </c>
+      <c r="P37">
+        <v>9.629999999999999</v>
+      </c>
+      <c r="Q37">
+        <v>11.82</v>
+      </c>
+      <c r="R37">
+        <v>17.68</v>
+      </c>
+      <c r="S37">
+        <v>11.02</v>
+      </c>
+      <c r="T37">
+        <v>14.61</v>
+      </c>
+      <c r="U37">
+        <v>11.36</v>
+      </c>
+      <c r="V37">
+        <v>7.870000000000001</v>
+      </c>
+      <c r="W37">
+        <v>14.97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23">
+      <c r="A38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C38" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" t="s">
+        <v>159</v>
+      </c>
+      <c r="F38" t="s">
+        <v>173</v>
+      </c>
+      <c r="G38" t="s">
+        <v>187</v>
+      </c>
+      <c r="H38" t="s">
+        <v>201</v>
+      </c>
+      <c r="I38" t="s">
+        <v>215</v>
+      </c>
+      <c r="J38" t="s">
+        <v>229</v>
+      </c>
+      <c r="K38" t="s">
+        <v>242</v>
+      </c>
+      <c r="L38" t="s">
+        <v>255</v>
+      </c>
+      <c r="M38" t="s">
+        <v>268</v>
+      </c>
+      <c r="N38" t="s">
+        <v>282</v>
+      </c>
+      <c r="O38" t="s">
+        <v>295</v>
+      </c>
+      <c r="P38" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>321</v>
+      </c>
+      <c r="R38" t="s">
+        <v>334</v>
+      </c>
+      <c r="S38" t="s">
+        <v>347</v>
+      </c>
+      <c r="T38" t="s">
+        <v>358</v>
+      </c>
+      <c r="U38" t="s">
+        <v>368</v>
+      </c>
+      <c r="V38" t="s">
+        <v>381</v>
+      </c>
+      <c r="W38" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B39" t="s">
+        <v>91</v>
+      </c>
+      <c r="C39" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>3.97</v>
+      </c>
+      <c r="H39">
+        <v>3.82</v>
+      </c>
+      <c r="I39">
+        <v>3.72</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>4.14</v>
+      </c>
+      <c r="O39">
+        <v>4.52</v>
+      </c>
+      <c r="P39">
+        <v>3.24</v>
+      </c>
+      <c r="Q39">
+        <v>4.84</v>
+      </c>
+      <c r="R39">
+        <v>7.340000000000001</v>
+      </c>
+      <c r="S39">
+        <v>5</v>
+      </c>
+      <c r="T39">
+        <v>6.39</v>
+      </c>
+      <c r="U39">
+        <v>5.88</v>
+      </c>
+      <c r="V39">
+        <v>4.18</v>
+      </c>
+      <c r="W39">
+        <v>7.42</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C40" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40">
+        <v>11.68</v>
+      </c>
+      <c r="E40">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="F40">
+        <v>11.25</v>
+      </c>
+      <c r="G40">
+        <v>12.03</v>
+      </c>
+      <c r="H40">
+        <v>10.9</v>
+      </c>
+      <c r="I40">
+        <v>5.34</v>
+      </c>
+      <c r="J40">
+        <v>3.79</v>
+      </c>
+      <c r="K40">
+        <v>6.49</v>
+      </c>
+      <c r="L40">
+        <v>5.44</v>
+      </c>
+      <c r="M40">
+        <v>3.67</v>
+      </c>
+      <c r="N40">
+        <v>4.17</v>
+      </c>
+      <c r="O40">
+        <v>4.35</v>
+      </c>
+      <c r="P40">
+        <v>7.96</v>
+      </c>
+      <c r="Q40">
+        <v>6.5</v>
+      </c>
+      <c r="R40">
+        <v>5.12</v>
+      </c>
+      <c r="S40">
+        <v>5.64</v>
+      </c>
+      <c r="T40">
+        <v>6.38</v>
+      </c>
+      <c r="U40">
+        <v>5.35</v>
+      </c>
+      <c r="V40">
+        <v>5.39</v>
+      </c>
+      <c r="W40">
+        <v>4.08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23">
+      <c r="A41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
+        <v>128</v>
+      </c>
+      <c r="D41" t="s">
+        <v>133</v>
+      </c>
+      <c r="E41" t="s">
+        <v>133</v>
+      </c>
+      <c r="F41" t="s">
+        <v>133</v>
+      </c>
+      <c r="G41" t="s">
+        <v>133</v>
+      </c>
+      <c r="H41" t="s">
+        <v>133</v>
+      </c>
+      <c r="I41" t="s">
+        <v>133</v>
+      </c>
+      <c r="J41" t="s">
+        <v>133</v>
+      </c>
+      <c r="K41" t="s">
+        <v>133</v>
+      </c>
+      <c r="L41" t="s">
+        <v>133</v>
+      </c>
+      <c r="M41" t="s">
+        <v>133</v>
+      </c>
+      <c r="N41" t="s">
+        <v>133</v>
+      </c>
+      <c r="O41" t="s">
+        <v>133</v>
+      </c>
+      <c r="P41" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>133</v>
+      </c>
+      <c r="R41" t="s">
+        <v>133</v>
+      </c>
+      <c r="S41" t="s">
+        <v>133</v>
+      </c>
+      <c r="T41" t="s">
+        <v>133</v>
+      </c>
+      <c r="U41" t="s">
+        <v>133</v>
+      </c>
+      <c r="V41" t="s">
+        <v>133</v>
+      </c>
+      <c r="W41" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B42" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" t="s">
+        <v>129</v>
+      </c>
+      <c r="D42">
+        <v>14.616</v>
+      </c>
+      <c r="E42">
+        <v>16.982</v>
+      </c>
+      <c r="F42">
+        <v>13.253</v>
+      </c>
+      <c r="G42">
+        <v>19.7</v>
+      </c>
+      <c r="H42">
+        <v>24.441</v>
+      </c>
+      <c r="I42">
+        <v>27.997</v>
+      </c>
+      <c r="J42">
+        <v>34.178</v>
+      </c>
+      <c r="K42">
+        <v>38.352</v>
+      </c>
+      <c r="L42">
+        <v>41.554</v>
+      </c>
+      <c r="M42">
+        <v>46.912</v>
+      </c>
+      <c r="N42">
+        <v>53.424</v>
+      </c>
+      <c r="O42">
+        <v>56.2</v>
+      </c>
+      <c r="P42">
+        <v>107.707</v>
+      </c>
+      <c r="Q42">
+        <v>121.703</v>
+      </c>
+      <c r="R42">
+        <v>141.841</v>
+      </c>
+      <c r="S42">
+        <v>145.881</v>
+      </c>
+      <c r="T42">
+        <v>149.577</v>
+      </c>
+      <c r="U42">
+        <v>158.025</v>
+      </c>
+      <c r="V42">
+        <v>149.871</v>
+      </c>
+      <c r="W42">
+        <v>156.531</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43">
+        <v>5</v>
+      </c>
+      <c r="E43">
+        <v>7</v>
+      </c>
+      <c r="F43">
+        <v>5</v>
+      </c>
+      <c r="G43">
+        <v>5</v>
+      </c>
+      <c r="H43">
+        <v>6</v>
+      </c>
+      <c r="I43">
+        <v>5</v>
+      </c>
+      <c r="J43">
+        <v>7</v>
+      </c>
+      <c r="K43">
+        <v>6</v>
+      </c>
+      <c r="L43">
+        <v>8</v>
+      </c>
+      <c r="M43">
+        <v>7</v>
+      </c>
+      <c r="N43">
+        <v>7</v>
+      </c>
+      <c r="O43">
+        <v>7</v>
+      </c>
+      <c r="P43">
+        <v>7</v>
+      </c>
+      <c r="Q43">
+        <v>6</v>
+      </c>
+      <c r="R43">
+        <v>9</v>
+      </c>
+      <c r="S43">
+        <v>5</v>
+      </c>
+      <c r="T43">
+        <v>9</v>
+      </c>
+      <c r="U43">
+        <v>5</v>
+      </c>
+      <c r="V43">
+        <v>6</v>
+      </c>
+      <c r="W43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" t="s">
+        <v>131</v>
+      </c>
+      <c r="D44" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" t="s">
+        <v>133</v>
+      </c>
+      <c r="F44" t="s">
+        <v>133</v>
+      </c>
+      <c r="G44" t="s">
+        <v>133</v>
+      </c>
+      <c r="H44" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" t="s">
+        <v>133</v>
+      </c>
+      <c r="J44" t="s">
+        <v>133</v>
+      </c>
+      <c r="K44" t="s">
+        <v>133</v>
+      </c>
+      <c r="L44" t="s">
+        <v>133</v>
+      </c>
+      <c r="M44" t="s">
+        <v>133</v>
+      </c>
+      <c r="N44" t="s">
+        <v>133</v>
+      </c>
+      <c r="O44" t="s">
+        <v>133</v>
+      </c>
+      <c r="P44" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>133</v>
+      </c>
+      <c r="R44" t="s">
+        <v>133</v>
+      </c>
+      <c r="S44" t="s">
+        <v>133</v>
+      </c>
+      <c r="T44" t="s">
+        <v>133</v>
+      </c>
+      <c r="U44" t="s">
+        <v>133</v>
+      </c>
+      <c r="V44" t="s">
+        <v>133</v>
+      </c>
+      <c r="W44" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" t="s">
+        <v>132</v>
+      </c>
+      <c r="D45">
+        <v>2.66</v>
+      </c>
+      <c r="E45">
+        <v>3.47</v>
+      </c>
+      <c r="F45">
+        <v>2.89</v>
+      </c>
+      <c r="G45">
+        <v>2.64</v>
+      </c>
+      <c r="H45">
+        <v>2.67</v>
+      </c>
+      <c r="I45">
+        <v>1.47</v>
+      </c>
+      <c r="J45">
+        <v>2.58</v>
+      </c>
+      <c r="K45">
+        <v>2.42</v>
+      </c>
+      <c r="L45">
+        <v>2.6</v>
+      </c>
+      <c r="M45">
+        <v>2.69</v>
+      </c>
+      <c r="N45">
+        <v>2.94</v>
+      </c>
+      <c r="O45">
+        <v>2.91</v>
+      </c>
+      <c r="P45">
+        <v>2.6</v>
+      </c>
+      <c r="Q45">
+        <v>4.3</v>
+      </c>
+      <c r="R45">
+        <v>5.68</v>
+      </c>
+      <c r="S45">
+        <v>6.07</v>
+      </c>
+      <c r="T45">
+        <v>6.6</v>
+      </c>
+      <c r="U45">
+        <v>6.83</v>
+      </c>
+      <c r="V45">
+        <v>6.46</v>
+      </c>
+      <c r="W45">
+        <v>7.02</v>
       </c>
     </row>
   </sheetData>
